--- a/docs/SalesHiker_Mobile_Test_Cases.xlsx
+++ b/docs/SalesHiker_Mobile_Test_Cases.xlsx
@@ -6,18 +6,21 @@
   <sheets>
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Login" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Notes" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Campaigns" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="338">
   <si>
     <t>SalesHiker Mobile Test Execution Summary</t>
   </si>
   <si>
+    <t>Updated 30-Oct-2026 from 5 automated run(s).</t>
+  </si>
+  <si>
     <t>Module</t>
   </si>
   <si>
@@ -45,19 +48,28 @@
     <t>Pass Rate (of executed)</t>
   </si>
   <si>
-    <t>Login</t>
+    <t>Login (mobile sign-in)</t>
+  </si>
+  <si>
+    <t>Campaigns (WhatsApp)</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>Counts update automatically when the Status or Mode columns on the Login sheet change.</t>
-  </si>
-  <si>
-    <t>Not Executed = cases with no PASS/FAIL in the selected run (for example, skipped because credentials were missing).</t>
-  </si>
-  <si>
-    <t>MLGN-012 is expected to FAIL until defect MLGN-D01 is fixed: its assertions describe the correct behaviour and must not be relaxed.</t>
+    <t>Counts are formulas over the Status and Mode columns of each module sheet.</t>
+  </si>
+  <si>
+    <t>Not Executed = no PASS/FAIL recorded yet (skipped tests and environment aborts are not results; see Comments).</t>
+  </si>
+  <si>
+    <t>Tests linked to an open defect (MLGN-012, MCMP-012, MCMP-019) are expected to FAIL until it is fixed: their assertions describe the correct behaviour.</t>
+  </si>
+  <si>
+    <t>Generated by tools\excel\update-workbooks.js after every run (scripts\run-*.ps1). Edit test-case text in tools\excel\modules\*.cases.js, not here.</t>
+  </si>
+  <si>
+    <t>Credentials are never written to this file; they come from config\.env (git-ignored).</t>
   </si>
   <si>
     <t>Req. ID #</t>
@@ -129,6 +141,9 @@
   </si>
   <si>
     <t>REQ-MAUTH-01</t>
+  </si>
+  <si>
+    <t>Login</t>
   </si>
   <si>
     <t>Workspace user (mobile app)</t>
@@ -153,8 +168,7 @@
   </si>
   <si>
     <t xml:space="preserve">Beta backend: accountsbeta.saleshiker.com
-Android 15 emulator (SalesHiker_API35, Pixel 7, x86_64)
-App: com.saleshiker.app 1.0.0 (saleshiker-beta-2026-10-28.apk)</t>
+Android device (see run summary)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Launch the app.
@@ -176,8 +190,8 @@
     <t>Home ("Today") dashboard opens with the "Unread chats" summary. Sign-in screen is no longer shown.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/smoke/login-smoke.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
+    <t xml:space="preserve">Spec: test/specs/smoke/login.spec.ts
+Not executed yet.</t>
   </si>
   <si>
     <t>MLGN-002</t>
@@ -198,8 +212,8 @@
     <t>Home ("Today") dashboard opens.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-enter-key.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
+    <t xml:space="preserve">Spec: test/specs/regression/login-valid.spec.ts
+Not executed yet.</t>
   </si>
   <si>
     <t>MLGN-003</t>
@@ -221,19 +235,6 @@
     <t>Equivalence Partitioning</t>
   </si>
   <si>
-    <t>Assertion is false: "Welcome back to SalesHiker" is visible</t>
-  </si>
-  <si>
-    <t>Run report: 20261029-175151-regression</t>
-  </si>
-  <si>
-    <t>Automation Suite (Maestro)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-email-uppercase.yaml
-Last automated run: 29-Oct-2026 FAIL (emulator-5554, Android 15) - 20261029-175151-regression</t>
-  </si>
-  <si>
     <t>MLGN-004</t>
   </si>
   <si>
@@ -253,16 +254,6 @@
     <t>Spaces are trimmed and the Home ("Today") dashboard opens.</t>
   </si>
   <si>
-    <t>Surrounding spaces ignored; Home opened.</t>
-  </si>
-  <si>
-    <t>Screenshot: MLGN-004-home.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-email-spaces.yaml
-Last automated run: 29-Oct-2026 PASS (emulator-5554, Android 15) - 20261029-175151-regression</t>
-  </si>
-  <si>
     <t>REQ-MAUTH-02</t>
   </si>
   <si>
@@ -294,8 +285,8 @@
     <t>Error banner "Email or password is wrong." is shown. User stays on the sign-in screen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-wrong-password.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
+    <t xml:space="preserve">Spec: test/specs/regression/login-invalid.spec.ts
+Not executed yet.</t>
   </si>
   <si>
     <t>MLGN-006</t>
@@ -322,10 +313,6 @@
     <t>The same generic error "Email or password is wrong." is shown (the app does not reveal whether the account exists). User stays on sign-in.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-unregistered-email.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
     <t>MLGN-007</t>
   </si>
   <si>
@@ -345,10 +332,6 @@
     <t>"Email or password is wrong." is shown. User is not signed in.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-password-case.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
     <t>REQ-MAUTH-03</t>
   </si>
   <si>
@@ -379,8 +362,8 @@
     <t>"Enter your email" and "Enter your password" are shown under the fields. No sign-in request ("Signing in..." is not shown).</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-empty-form.yaml
-Last automated run: 29-Oct-2026 FAIL (emulator-5554, Android 15) - 20261029-175151-regression</t>
+    <t xml:space="preserve">Spec: test/specs/regression/login-validation.spec.ts
+Not executed yet.</t>
   </si>
   <si>
     <t>MLGN-009</t>
@@ -402,16 +385,6 @@
     <t>Only "Enter your email" is shown. User stays on sign-in.</t>
   </si>
   <si>
-    <t>Only the email-required message shown.</t>
-  </si>
-  <si>
-    <t>N/A (passed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-email-required.yaml
-Last automated run: 29-Oct-2026 PASS (emulator-5554, Android 15) - 20261029-175151-regression</t>
-  </si>
-  <si>
     <t>MLGN-010</t>
   </si>
   <si>
@@ -431,10 +404,6 @@
     <t>Only "Enter your password" is shown. User stays on sign-in.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-password-required.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
     <t>MLGN-011</t>
   </si>
   <si>
@@ -452,10 +421,6 @@
   </si>
   <si>
     <t>Inline error "Enter a full email, like you@company.com." is shown under the email field. User stays on sign-in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-malformed-email.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
   </si>
   <si>
     <t>MLGN-012</t>
@@ -474,10 +439,6 @@
     <t>Only the inline format error is shown. The form is not submitted: no "Signing in..." state and no server error banner. Empty fields are already handled this way (MLGN-008).</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-malformed-email-not-sent.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
     <t>REQ-MAUTH-04</t>
   </si>
   <si>
@@ -505,8 +466,8 @@
     <t>Input is rejected as a malformed email ("Enter a full email, like you@company.com."). User is not signed in and the app does not crash.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-injection.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
+    <t xml:space="preserve">Spec: test/specs/regression/login-robustness.spec.ts
+Not executed yet.</t>
   </si>
   <si>
     <t>MLGN-014</t>
@@ -531,10 +492,6 @@
     <t>"Enter your password" is shown and no sign-in is attempted ("Email or password is wrong." does not appear).</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-whitespace-password.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
     <t>MLGN-015</t>
   </si>
   <si>
@@ -554,10 +511,6 @@
     <t>Sign-in is refused with an error message and the app stays responsive on the sign-in screen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-long-email.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
     <t>REQ-MAUTH-05</t>
   </si>
   <si>
@@ -583,8 +536,8 @@
     <t>Logo, "Welcome back to SalesHiker", Email address, Password, "Show password", "Sign in", "Forgot password?", "Scan a code from the web app", "New here? Create your workspace" and the dark-mode toggle are visible.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/smoke/app-launch.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
+    <t xml:space="preserve">Spec: test/specs/smoke/app-launch.spec.ts
+Not executed yet.</t>
   </si>
   <si>
     <t>MLGN-017</t>
@@ -605,8 +558,8 @@
     <t>Password is masked, then shown as plain text (button label "Hide password"), then masked again (label "Show password").</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-password-visibility.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
+    <t xml:space="preserve">Spec: test/specs/regression/login-options.spec.ts
+Not executed yet.</t>
   </si>
   <si>
     <t>MLGN-018</t>
@@ -622,10 +575,6 @@
     <t>The password-reset page (accountsbeta.saleshiker.com) opens in the device browser and the app leaves the sign-in screen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-forgot-password.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
     <t>MLGN-019</t>
   </si>
   <si>
@@ -637,16 +586,6 @@
   </si>
   <si>
     <t>The sign-up page (accountsbeta.saleshiker.com) opens in the device browser.</t>
-  </si>
-  <si>
-    <t>Hand-off to the browser happened (Chrome opened).</t>
-  </si>
-  <si>
-    <t>Screenshot: MLGN-019-handoff.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-create-workspace.yaml
-Last automated run: 29-Oct-2026 PASS (emulator-5554, Android 15) - 20261029-175151-regression</t>
   </si>
   <si>
     <t>REQ-MAUTH-06</t>
@@ -672,8 +611,8 @@
     <t>Home ("Today") opens directly. The user is not asked to sign in again.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-session-restart.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
+    <t xml:space="preserve">Spec: test/specs/regression/session.spec.ts
+Not executed yet.</t>
   </si>
   <si>
     <t>MLGN-021</t>
@@ -688,16 +627,6 @@
   </si>
   <si>
     <t>Back sends the app to the background (it does not return to the sign-in screen). Reopening shows Home, still signed in.</t>
-  </si>
-  <si>
-    <t>Back left the app; reopening showed Home.</t>
-  </si>
-  <si>
-    <t>Screenshot: MLGN-021-home-after-relaunch.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-back-keeps-session.yaml
-Last automated run: 29-Oct-2026 PASS (emulator-5554, Android 15) - 20261029-175151-regression</t>
   </si>
   <si>
     <t>REQ-MAUTH-07</t>
@@ -724,10 +653,6 @@
     <t>Dialog "Sign out?" with "You stop getting notifications on this phone." and Cancel / Sign out buttons. After Cancel the dialog closes and the user stays signed in on More.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-signout-cancel.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
     <t>MLGN-023</t>
   </si>
   <si>
@@ -741,10 +666,6 @@
   </si>
   <si>
     <t>After confirming, the sign-in screen is shown. After relaunch the sign-in screen is still shown (Home is not reachable).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-signout.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
   </si>
   <si>
     <t>REQ-MAUTH-08</t>
@@ -781,59 +702,474 @@
     <t>"Check your connection and try again." is shown. User stays on sign-in; nothing is lost.</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow: .maestro/flows/regression/login-offline.yaml
-Not executed: the device went offline during run 20261029-175151-regression (environment, not a product result).</t>
-  </si>
-  <si>
-    <t>How to use this workbook</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Generated file</t>
-  </si>
-  <si>
-    <t>Rebuilt by tools\excel\build-login-workbooks.js from tools\excel\login-test-cases.js and the selected run folder(s). Edit test-case text in login-test-cases.js, not here, or it is overwritten on the next build.</t>
-  </si>
-  <si>
-    <t>Columns filled from the run</t>
-  </si>
-  <si>
-    <t>Actual Result, Screenshot / Video, Status, Test Iteration, Test Executed By, Date of Execution, Comments.</t>
-  </si>
-  <si>
-    <t>Summary sheet</t>
-  </si>
-  <si>
-    <t>Counts are formulas over the Status and Mode columns of the Login sheet.</t>
-  </si>
-  <si>
-    <t>"Automation Suite (Maestro)" means the Maestro flows in .maestro\flows of this project, run with scripts\run-regression.ps1 -Tags login. Evidence (screenshots, video, logs, junit.xml) is under reports\&lt;timestamp&gt;-&lt;suite&gt;\.</t>
-  </si>
-  <si>
-    <t>Beta backend: accountsbeta.saleshiker.com; Android 15 emulator (SalesHiker_API35, Pixel 7, x86_64); App: com.saleshiker.app 1.0.0 (saleshiker-beta-2026-10-28.apk)</t>
-  </si>
-  <si>
-    <t>Credentials</t>
-  </si>
-  <si>
-    <t>Credentials are never written in this file. They come from config\.env (git-ignored), and the runner redacts the password from all text reports.</t>
-  </si>
-  <si>
-    <t>1 = first execution cycle. 2 = re-test after a failure.</t>
-  </si>
-  <si>
-    <t>Relation to the web workbook</t>
-  </si>
-  <si>
-    <t>Same columns and conventions as D:\QA\Automation\SalesHiker\docs\test-cases\SalesHiker_Test_Cases.xlsx (web app). Mobile IDs use the MLGN- prefix so they never clash with the web LGN- IDs.</t>
-  </si>
-  <si>
-    <t>Defects</t>
-  </si>
-  <si>
-    <t>See docs\SalesHiker_Mobile_Defect_Tracker.xlsx (sheet Login). IDs: MLGN-Dnn.</t>
+    <t xml:space="preserve">Spec: test/specs/regression/network.spec.ts
+Not executed yet.</t>
+  </si>
+  <si>
+    <t>REQ-MCMP-01</t>
+  </si>
+  <si>
+    <t>Campaigns</t>
+  </si>
+  <si>
+    <t>Signed-in workspace user (mobile app)</t>
+  </si>
+  <si>
+    <t>TS-MCMP-01</t>
+  </si>
+  <si>
+    <t>Campaign list shows the account's campaigns</t>
+  </si>
+  <si>
+    <t>MCMP-001</t>
+  </si>
+  <si>
+    <t>Campaign list opens from More with search, filters and campaigns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registered beta test account (config\.env) with at least one WhatsApp campaign.
+User is signed in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta backend: accountsbeta.saleshiker.com
+DQCI7XBU5LXWB6KZ (RMX3997, Android 16); app com.saleshiker.app 1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open More.
+2. Tap "Campaigns" (WHATSAPP section).</t>
+  </si>
+  <si>
+    <t>Test account from config\.env. Campaign data: live beta account data.</t>
+  </si>
+  <si>
+    <t>Campaigns screen opens: title with the total count, "Search campaigns" field, filter chips All / Drip / Retarget / Active / Paused with counts, "All" selected, and at least one campaign row.</t>
+  </si>
+  <si>
+    <t>Campaign list shown with count, search, five filter chips ("All" selected) and campaign rows.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-001_campaign_list.png</t>
+  </si>
+  <si>
+    <t>Automation Suite (Appium + WebdriverIO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/smoke/campaigns.spec.ts
+Last result: PASS on 30-Oct-2026, run 20261030-171502-full.
+History (latest first): 30-Oct-2026 PASS, 30-Oct-2026 PASS, 30-Oct-2026 PASS</t>
+  </si>
+  <si>
+    <t>MCMP-002</t>
+  </si>
+  <si>
+    <t>Each row shows name, date, type, enrolled, sent and status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registered beta test account (config\.env) with at least one WhatsApp campaign.
+App restarted signed in (signs in only if the session is gone).
+More &gt; Campaigns is open, "All" selected, search empty.</t>
+  </si>
+  <si>
+    <t>1. Read every row of the list (scroll to the end).</t>
+  </si>
+  <si>
+    <t>Every row shows the campaign name, start date, type (Drip / Retarget), "&lt;n&gt; enrolled, &lt;n&gt; sent" and a status pill (Active / Paused); sent never exceeds enrolled. The list ends with "End of list. Edit steps or build new campaigns on the web app."</t>
+  </si>
+  <si>
+    <t>All rows had name, date, type, enrolled/sent counts and status; end-of-list footer shown.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-002_rows.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/campaigns-list.spec.ts
+Last result: PASS on 30-Oct-2026, run 20261030-171502-full.
+History (latest first): 30-Oct-2026 PASS, 30-Oct-2026 PASS</t>
+  </si>
+  <si>
+    <t>MCMP-003</t>
+  </si>
+  <si>
+    <t>Header count and "All" chip count match the number of campaigns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Read the count under the title.
+2. Read the count on the "All" chip.
+3. Count the rows (scroll to the end).</t>
+  </si>
+  <si>
+    <t>Both counts equal the number of rows.</t>
+  </si>
+  <si>
+    <t>Header count, "All" count and row count were equal.</t>
+  </si>
+  <si>
+    <t>Run report: 20261030-171502-full</t>
+  </si>
+  <si>
+    <t>TS-MCMP-02</t>
+  </si>
+  <si>
+    <t>Filters narrow the list by type and status</t>
+  </si>
+  <si>
+    <t>MCMP-004</t>
+  </si>
+  <si>
+    <t>Type filters show only campaigns of that type and match the chip count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note all rows.
+2. Tap "Drip"; read the rows.
+3. Tap "Retarget"; read the rows.</t>
+  </si>
+  <si>
+    <t>Each filter shows only campaigns of that type, as many as its chip count and as many as the unfiltered list has of that type.</t>
+  </si>
+  <si>
+    <t>Drip and Retarget showed only their own campaigns, matching chip counts.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-004_Drip.png</t>
+  </si>
+  <si>
+    <t>MCMP-005</t>
+  </si>
+  <si>
+    <t>Status filters show only campaigns with that status and match the chip count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note all rows.
+2. Tap "Active"; read the rows.
+3. Scroll the chips and tap "Paused"; read the rows.</t>
+  </si>
+  <si>
+    <t>Each filter shows only campaigns with that status, as many as its chip count and as many as the unfiltered list has with that status.</t>
+  </si>
+  <si>
+    <t>Active and Paused showed only their own campaigns, matching chip counts.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-005_Active.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/campaigns-list.spec.ts
+Last result: PASS on 30-Oct-2026, run 20261030-171502-full.
+History (latest first): 30-Oct-2026 PASS, 30-Oct-2026 FAIL</t>
+  </si>
+  <si>
+    <t>MCMP-006</t>
+  </si>
+  <si>
+    <t>Selected filter is marked and "All" restores the full list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tap "Paused".
+2. Tap "All".</t>
+  </si>
+  <si>
+    <t>The tapped chip is highlighted (selected); after "All" the full list is back.</t>
+  </si>
+  <si>
+    <t>Selected chip highlighted; "All" restored every row.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-006_paused_selected.png</t>
+  </si>
+  <si>
+    <t>MCMP-007</t>
+  </si>
+  <si>
+    <t>Filter is kept after opening a campaign and resets when the list is reopened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tap "Active".
+2. Open the first campaign, then tap Back.
+3. Tap Back to More, then open Campaigns again.</t>
+  </si>
+  <si>
+    <t>After Back from the detail, "Active" is still selected with the same rows. After reopening from More, "All" is selected.</t>
+  </si>
+  <si>
+    <t>Filter kept after detail; reset to "All" after reopening.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-007_reopened_list.png</t>
+  </si>
+  <si>
+    <t>TS-MCMP-03</t>
+  </si>
+  <si>
+    <t>Search finds campaigns</t>
+  </si>
+  <si>
+    <t>MCMP-008</t>
+  </si>
+  <si>
+    <t>Search by part of a name is case-insensitive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Take a word from a campaign name.
+2. Type it in UPPER CASE in "Search campaigns".</t>
+  </si>
+  <si>
+    <t>Search: a word from an existing campaign name, in upper case (read from the list at run time).</t>
+  </si>
+  <si>
+    <t>Exactly the campaigns whose name contains the word (any case) are listed.</t>
+  </si>
+  <si>
+    <t>Upper-case search listed every campaign containing the word.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-008_upper-case_search.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/campaigns-search.spec.ts
+Last result: PASS on 30-Oct-2026, run 20261030-171502-full.
+History (latest first): 30-Oct-2026 PASS, 30-Oct-2026 PASS</t>
+  </si>
+  <si>
+    <t>MCMP-009</t>
+  </si>
+  <si>
+    <t>Search updates the filter chip counts to the matching campaigns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Type a word from a campaign name in "Search campaigns".
+2. Read the chip counts and the title.</t>
+  </si>
+  <si>
+    <t>Search: a word from an existing campaign name (read from the list at run time).</t>
+  </si>
+  <si>
+    <t>Each chip counts only the matching campaigns; the total under the title is hidden while searching.</t>
+  </si>
+  <si>
+    <t>Chip counts matched the search results; title count hidden.</t>
+  </si>
+  <si>
+    <t>MCMP-010</t>
+  </si>
+  <si>
+    <t>No match shows the empty state and Clear Filters resets search and filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tap "Drip".
+2. Search for a name that does not exist.
+3. Tap "Clear Filters".</t>
+  </si>
+  <si>
+    <t>Search: qa-no-such-campaign-zz</t>
+  </si>
+  <si>
+    <t>"No campaigns found" and "Try another name, type or status." with a "Clear Filters" button; all chip counts 0. Clear Filters empties the search, selects "All" and shows every campaign.</t>
+  </si>
+  <si>
+    <t>Empty state shown; Clear Filters restored the full list with "All" selected.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-010_empty_state.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/campaigns-search.spec.ts
+Last result: PASS on 30-Oct-2026, run 20261030-171502-full.
+History (latest first): 30-Oct-2026 PASS, 30-Oct-2026 FAIL</t>
+  </si>
+  <si>
+    <t>MCMP-011</t>
+  </si>
+  <si>
+    <t>Clear search (X) restores the full list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search for a name that does not exist.
+2. Tap the X in the search field.</t>
+  </si>
+  <si>
+    <t>The search field is empty and every campaign is listed again.</t>
+  </si>
+  <si>
+    <t>Search cleared; full list shown.</t>
+  </si>
+  <si>
+    <t>MCMP-012</t>
+  </si>
+  <si>
+    <t>Search finds campaigns by type and status, as the empty-state hint says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search "drip", "retarget", "active" and "paused" in turn.
+2. Compare with the campaigns of that type/status.</t>
+  </si>
+  <si>
+    <t>Search: drip, retarget, active, paused</t>
+  </si>
+  <si>
+    <t>The empty state tells users to "Try another name, type or status.", so each search lists every campaign of that type or status.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">searches that miss campaigns of that type/status: expected [ '"drip": 1 of 5', …(2) ] to deeply equal []
+Defect: MCMP-D02</t>
+  </si>
+  <si>
+    <t>Screenshot: MCMP-012_Search_finds_campaigns_by_type_and_status_as_the_empty-state_hint_says/screenshot.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/campaigns-search.spec.ts
+Last result: FAIL on 30-Oct-2026, run 20261030-173959-single-MCMP-012, defect MCMP-D02.
+History (latest first): 30-Oct-2026 FAIL, 30-Oct-2026 FAIL, 30-Oct-2026 FAIL, 30-Oct-2026 FAIL</t>
+  </si>
+  <si>
+    <t>TS-MCMP-04</t>
+  </si>
+  <si>
+    <t>Campaign detail shows the campaign's state and results</t>
+  </si>
+  <si>
+    <t>MCMP-013</t>
+  </si>
+  <si>
+    <t>Detail opens with the name, status, type and enrolment of the tapped row</t>
+  </si>
+  <si>
+    <t>1. Tap the first campaign.</t>
+  </si>
+  <si>
+    <t>Title is the campaign name; the summary shows the same status, "&lt;type&gt;, started &lt;date&gt;" and "&lt;n&gt; enrolled: &lt;n&gt; active, &lt;n&gt; done" matching the row (active + done = enrolled).</t>
+  </si>
+  <si>
+    <t>Detail title, status, type, start date and enrolment matched the list row.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-013_detail.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/campaign-detail.spec.ts
+Last result: PASS on 30-Oct-2026, run 20261030-171502-full.
+History (latest first): 30-Oct-2026 PASS, 30-Oct-2026 PASS</t>
+  </si>
+  <si>
+    <t>MCMP-014</t>
+  </si>
+  <si>
+    <t>Delivery tiles agree with the list and their percentages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a campaign that has sent messages.
+2. Read the DELIVERY tiles.</t>
+  </si>
+  <si>
+    <t>Sent equals the row's "sent"; Delivered, Read and Failed are at most Sent and their % = count / Sent (rounded); Read &lt;= Delivered.</t>
+  </si>
+  <si>
+    <t>Delivery tiles consistent with the list and with each other.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-014_delivery.png</t>
+  </si>
+  <si>
+    <t>MCMP-015</t>
+  </si>
+  <si>
+    <t>Campaign with nobody enrolled shows no delivery stats and "No recipients yet"</t>
+  </si>
+  <si>
+    <t>1. Open a campaign with 0 enrolled.</t>
+  </si>
+  <si>
+    <t>No DELIVERY section; RECENT RECIPIENTS shows "No recipients yet".</t>
+  </si>
+  <si>
+    <t>No delivery section; "No recipients yet" shown.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-015_empty_campaign.png</t>
+  </si>
+  <si>
+    <t>MCMP-016</t>
+  </si>
+  <si>
+    <t>Detail lists the steps and says edits are made on the web app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the first campaign.
+2. Read STEPS and the note at the bottom.</t>
+  </si>
+  <si>
+    <t>STEPS lists numbered steps; the note "Edit steps, pause or resume campaigns on the web app." is shown (no edit controls on mobile).</t>
+  </si>
+  <si>
+    <t>Numbered steps and the web-app note shown.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-016_steps.png</t>
+  </si>
+  <si>
+    <t>MCMP-017</t>
+  </si>
+  <si>
+    <t>A recipient opens the contact profile and Back returns to the campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a campaign with enrolments.
+2. Tap the first recent recipient.
+3. Press Back.</t>
+  </si>
+  <si>
+    <t>The recipient's contact profile opens (WhatsApp / Call / Add Task / Edit actions); Back returns to the same campaign.</t>
+  </si>
+  <si>
+    <t>Contact profile opened; Back returned to the campaign.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-017_contact_profile.png</t>
+  </si>
+  <si>
+    <t>MCMP-018</t>
+  </si>
+  <si>
+    <t>Back goes from detail to the list and from the list to More</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a campaign.
+2. Tap Back.
+3. Tap Back again.</t>
+  </si>
+  <si>
+    <t>First Back shows the campaign list; second Back shows More.</t>
+  </si>
+  <si>
+    <t>Back navigation: detail &gt; list &gt; More.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MCMP-018_back_on_More.png</t>
+  </si>
+  <si>
+    <t>MCMP-019</t>
+  </si>
+  <si>
+    <t>Recipients who replied are counted as delivered and read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open each campaign that has sent messages.
+2. Count recipients marked "Replied".
+3. Read the Delivered and Read tiles.</t>
+  </si>
+  <si>
+    <t>A reply means the message reached and was seen by the contact, so Delivered and Read are each at least the number of recipients who replied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivered (1 replied): expected +0 to be at least 1
+Defect: MCMP-D01</t>
+  </si>
+  <si>
+    <t>Screenshot: MCMP-019_Recipients_who_replied_are_counted_as_delivered_and_read/screenshot.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/campaign-detail.spec.ts
+Last result: FAIL on 30-Oct-2026, run 20261030-171502-full, defect MCMP-D01.
+History (latest first): 30-Oct-2026 FAIL, 30-Oct-2026 FAIL</t>
   </si>
 </sst>
 </file>
@@ -844,7 +1180,7 @@
     <numFmt numFmtId="164" formatCode="0.0%;-0.0%;-"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -858,8 +1194,19 @@
       <name val="Arial"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -870,33 +1217,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0563C1"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -941,60 +1267,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1352,10 +1691,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,124 +1703,181 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5">
         <f>C4+D4</f>
         <v>24</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <f>COUNTIF('Login'!U2:U75,"Automation")</f>
         <v>24</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <f>COUNTIF('Login'!U2:U75,"Manual")</f>
         <v>0</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <f>F4+G4</f>
-        <v>6</v>
-      </c>
-      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
         <f>COUNTIF('Login'!Q2:Q75,"PASS")</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
         <f>COUNTIF('Login'!Q2:Q75,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <f>B4-E4</f>
+        <v>24</v>
+      </c>
+      <c r="I4" s="6">
+        <f>IF(E4=0,0,F4/E4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="5">
+        <f>C5+D5</f>
+        <v>19</v>
+      </c>
+      <c r="C5" s="5">
+        <f>COUNTIF('Campaigns'!U2:U70,"Automation")</f>
+        <v>19</v>
+      </c>
+      <c r="D5" s="5">
+        <f>COUNTIF('Campaigns'!U2:U70,"Manual")</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <f>F5+G5</f>
+        <v>19</v>
+      </c>
+      <c r="F5" s="5">
+        <f>COUNTIF('Campaigns'!Q2:Q70,"PASS")</f>
+        <v>17</v>
+      </c>
+      <c r="G5" s="5">
+        <f>COUNTIF('Campaigns'!Q2:Q70,"FAIL")</f>
         <v>2</v>
       </c>
-      <c r="H4" s="4">
-        <f>B4-E4</f>
+      <c r="H5" s="5">
+        <f>B5-E5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <f>IF(E5=0,0,F5/E5)</f>
+        <v>0.8947368421052632</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="8">
+        <f>SUM(B4:B5)</f>
+        <v>43</v>
+      </c>
+      <c r="C6" s="8">
+        <f>SUM(C4:C5)</f>
+        <v>43</v>
+      </c>
+      <c r="D6" s="8">
+        <f>SUM(D4:D5)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <f>SUM(E4:E5)</f>
+        <v>19</v>
+      </c>
+      <c r="F6" s="8">
+        <f>SUM(F4:F5)</f>
+        <v>17</v>
+      </c>
+      <c r="G6" s="8">
+        <f>SUM(G4:G5)</f>
+        <v>2</v>
+      </c>
+      <c r="H6" s="8">
+        <f>SUM(H4:H5)</f>
+        <v>24</v>
+      </c>
+      <c r="I6" s="9">
+        <f>IF(E6=0,0,F6/E6)</f>
+        <v>0.8947368421052632</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="5">
-        <f>IF(E4=0,0,F4/E4)</f>
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="7">
-        <f>SUM(B4:B4)</f>
-        <v>24</v>
-      </c>
-      <c r="C5" s="7">
-        <f>SUM(C4:C4)</f>
-        <v>24</v>
-      </c>
-      <c r="D5" s="7">
-        <f>SUM(D4:D4)</f>
-      </c>
-      <c r="E5" s="7">
-        <f>SUM(E4:E4)</f>
-        <v>6</v>
-      </c>
-      <c r="F5" s="7">
-        <f>SUM(F4:F4)</f>
-        <v>4</v>
-      </c>
-      <c r="G5" s="7">
-        <f>SUM(G4:G4)</f>
-        <v>2</v>
-      </c>
-      <c r="H5" s="7">
-        <f>SUM(H4:H4)</f>
-        <v>18</v>
-      </c>
-      <c r="I5" s="8">
-        <f>IF(E5=0,0,F5/E5)</f>
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>14</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" location="#'Login'!A1"/>
+    <hyperlink ref="A5" r:id="rId2" location="#'Campaigns'!A1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1509,119 +1905,119 @@
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="42" customWidth="1"/>
+    <col min="22" max="22" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="62" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S1" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T1" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U1" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="V1" s="10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
@@ -1630,54 +2026,54 @@
       <c r="S2" s="11"/>
       <c r="T2" s="13"/>
       <c r="U2" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="11" t="s">
+      <c r="L3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>48</v>
-      </c>
       <c r="N3" s="11" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
@@ -1686,190 +2082,166 @@
       <c r="S3" s="11"/>
       <c r="T3" s="13"/>
       <c r="U3" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="M4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="11" t="s">
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V4" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="R4" s="11">
-        <v>1</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T4" s="13">
-        <v>46324.51960648148</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="11" t="s">
+      <c r="N5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V5" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="R5" s="11">
-        <v>1</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T5" s="13">
-        <v>46324.51821759259</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="V5" s="11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="H6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="K6" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="L6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="N6" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
@@ -1878,54 +2250,54 @@
       <c r="S6" s="11"/>
       <c r="T6" s="13"/>
       <c r="U6" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>76</v>
-      </c>
       <c r="F7" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="I7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="K7" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="L7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>89</v>
       </c>
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
@@ -1934,54 +2306,54 @@
       <c r="S7" s="11"/>
       <c r="T7" s="13"/>
       <c r="U7" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>76</v>
-      </c>
       <c r="F8" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="L8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N8" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>95</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -1990,190 +2362,166 @@
       <c r="S8" s="11"/>
       <c r="T8" s="13"/>
       <c r="U8" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="H9" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="K9" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="L9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="11" t="s">
         <v>102</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="R9" s="11">
-        <v>1</v>
-      </c>
-      <c r="S9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T9" s="13">
-        <v>46324.52086805555</v>
-      </c>
-      <c r="U9" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="11" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F10" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="N10" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="R10" s="11">
-        <v>1</v>
-      </c>
-      <c r="S10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T10" s="13">
-        <v>46324.517534722225</v>
-      </c>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="13"/>
       <c r="U10" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -2182,54 +2530,54 @@
       <c r="S11" s="11"/>
       <c r="T11" s="13"/>
       <c r="U11" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -2238,54 +2586,54 @@
       <c r="S12" s="11"/>
       <c r="T12" s="13"/>
       <c r="U12" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -2294,54 +2642,54 @@
       <c r="S13" s="11"/>
       <c r="T13" s="13"/>
       <c r="U13" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -2350,54 +2698,54 @@
       <c r="S14" s="11"/>
       <c r="T14" s="13"/>
       <c r="U14" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -2406,54 +2754,54 @@
       <c r="S15" s="11"/>
       <c r="T15" s="13"/>
       <c r="U15" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -2462,54 +2810,54 @@
       <c r="S16" s="11"/>
       <c r="T16" s="13"/>
       <c r="U16" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -2518,54 +2866,54 @@
       <c r="S17" s="11"/>
       <c r="T17" s="13"/>
       <c r="U17" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="K18" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="11" t="s">
+      <c r="L18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="11" t="s">
         <v>155</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N18" s="11" t="s">
-        <v>167</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
@@ -2574,54 +2922,54 @@
       <c r="S18" s="11"/>
       <c r="T18" s="13"/>
       <c r="U18" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="K19" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>172</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
@@ -2630,122 +2978,110 @@
       <c r="S19" s="11"/>
       <c r="T19" s="13"/>
       <c r="U19" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="11" t="s">
         <v>156</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N20" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="O20" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="P20" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q20" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="R20" s="11">
-        <v>1</v>
-      </c>
-      <c r="S20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T20" s="13">
-        <v>46324.51672453704</v>
-      </c>
-      <c r="U20" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="11" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
@@ -2754,122 +3090,110 @@
       <c r="S21" s="11"/>
       <c r="T21" s="13"/>
       <c r="U21" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="O22" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="P22" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q22" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="R22" s="11">
-        <v>1</v>
-      </c>
-      <c r="S22" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T22" s="13">
-        <v>46324.51568287037</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="13"/>
       <c r="U22" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
@@ -2878,54 +3202,54 @@
       <c r="S23" s="11"/>
       <c r="T23" s="13"/>
       <c r="U23" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="O24" s="11"/>
       <c r="P24" s="11"/>
@@ -2934,54 +3258,54 @@
       <c r="S24" s="11"/>
       <c r="T24" s="13"/>
       <c r="U24" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="O25" s="11"/>
       <c r="P25" s="11"/>
@@ -2990,10 +3314,10 @@
       <c r="S25" s="11"/>
       <c r="T25" s="13"/>
       <c r="U25" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="12:21" x14ac:dyDescent="0.25"/>
@@ -3047,7 +3371,7 @@
     <row r="74" spans="12:21" x14ac:dyDescent="0.25"/>
     <row r="75" spans="12:21" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:V25"/>
+  <autoFilter ref="A1:V75"/>
   <conditionalFormatting sqref="Q2:Q75">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"PASS"</formula>
@@ -3082,13 +3406,6 @@
       <formula1>"Manual,Automation,Removed"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="P4" r:id="rId1"/>
-    <hyperlink ref="P5" r:id="rId2"/>
-    <hyperlink ref="P9" r:id="rId3"/>
-    <hyperlink ref="P20" r:id="rId4"/>
-    <hyperlink ref="P22" r:id="rId5"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3096,94 +3413,1496 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="48" customWidth="1"/>
+    <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="15" width="40" customWidth="1"/>
+    <col min="16" max="16" width="34" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" ht="62" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" s="11">
+        <v>3</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T2" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="P3" s="14" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="Q3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R3" s="11">
+        <v>2</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T3" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="B2" s="16" t="s">
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="G4" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="H4" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="K4" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="O4" s="11" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="P4" s="14" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="Q4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" s="11">
+        <v>2</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T4" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="E5" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="F5" s="11" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="G5" s="11" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="H5" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="K5" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="11" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="O5" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="P5" s="14" t="s">
         <v>235</v>
       </c>
-    </row>
+      <c r="Q5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R5" s="11">
+        <v>2</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T5" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R6" s="11">
+        <v>2</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T6" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="11">
+        <v>2</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T7" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R8" s="11">
+        <v>2</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T8" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R9" s="11">
+        <v>2</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T9" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R10" s="11">
+        <v>2</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T10" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q11" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R11" s="11">
+        <v>2</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T11" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q12" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R12" s="11">
+        <v>2</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T12" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="11">
+        <v>4</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T13" s="13">
+        <v>46325.50694328704</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R14" s="11">
+        <v>2</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T14" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R15" s="11">
+        <v>2</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T15" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R16" s="11">
+        <v>2</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T16" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R17" s="11">
+        <v>2</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T17" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R18" s="11">
+        <v>2</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T18" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R19" s="11">
+        <v>2</v>
+      </c>
+      <c r="S19" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T19" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V19" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="11">
+        <v>2</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="T20" s="13">
+        <v>46325.48961690972</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="21" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="12:21" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <autoFilter ref="A1:V70"/>
+  <conditionalFormatting sqref="Q2:Q70">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" sqref="L10:L70">
+      <formula1>"Smoke,Functional,Regression,UAT,API"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="L2:L70">
+      <formula1>"Smoke,Functional,Regression,UAT,API"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="M10:M70">
+      <formula1>"Positive,Negative,Boundary Value,Equivalence Partitioning,Error Handling,Validation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="M2:M70">
+      <formula1>"Positive,Negative,Boundary Value,Equivalence Partitioning,Error Handling,Validation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="Q10:Q70">
+      <formula1>"PASS,FAIL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="Q2:Q70">
+      <formula1>"PASS,FAIL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="U10:U70">
+      <formula1>"Manual,Automation,Removed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="U2:U70">
+      <formula1>"Manual,Automation,Removed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="P2" r:id="rId1"/>
+    <hyperlink ref="P3" r:id="rId2"/>
+    <hyperlink ref="P4" r:id="rId3"/>
+    <hyperlink ref="P5" r:id="rId4"/>
+    <hyperlink ref="P6" r:id="rId5"/>
+    <hyperlink ref="P7" r:id="rId6"/>
+    <hyperlink ref="P8" r:id="rId7"/>
+    <hyperlink ref="P9" r:id="rId8"/>
+    <hyperlink ref="P10" r:id="rId9"/>
+    <hyperlink ref="P11" r:id="rId10"/>
+    <hyperlink ref="P12" r:id="rId11"/>
+    <hyperlink ref="P13" r:id="rId12"/>
+    <hyperlink ref="P14" r:id="rId13"/>
+    <hyperlink ref="P15" r:id="rId14"/>
+    <hyperlink ref="P16" r:id="rId15"/>
+    <hyperlink ref="P17" r:id="rId16"/>
+    <hyperlink ref="P18" r:id="rId17"/>
+    <hyperlink ref="P19" r:id="rId18"/>
+    <hyperlink ref="P20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/SalesHiker_Mobile_Test_Cases.xlsx
+++ b/docs/SalesHiker_Mobile_Test_Cases.xlsx
@@ -7,18 +7,19 @@
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Login" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Campaigns" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Broadcasts" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="438">
   <si>
     <t>SalesHiker Mobile Test Execution Summary</t>
   </si>
   <si>
-    <t>Updated 30-Oct-2026 from 5 automated run(s).</t>
+    <t>Updated 31-Oct-2026 from 6 automated run(s).</t>
   </si>
   <si>
     <t>Module</t>
@@ -52,6 +53,9 @@
   </si>
   <si>
     <t>Campaigns (WhatsApp)</t>
+  </si>
+  <si>
+    <t>Broadcasts (WhatsApp)</t>
   </si>
   <si>
     <t>Total</t>
@@ -1170,6 +1174,336 @@
     <t xml:space="preserve">Spec: test/specs/regression/campaign-detail.spec.ts
 Last result: FAIL on 30-Oct-2026, run 20261030-171502-full, defect MCMP-D01.
 History (latest first): 30-Oct-2026 FAIL, 30-Oct-2026 FAIL</t>
+  </si>
+  <si>
+    <t>REQ-MBRD-01</t>
+  </si>
+  <si>
+    <t>Broadcasts</t>
+  </si>
+  <si>
+    <t>TS-MBRD-01</t>
+  </si>
+  <si>
+    <t>Broadcast list and entry to the wizard</t>
+  </si>
+  <si>
+    <t>MBRD-001</t>
+  </si>
+  <si>
+    <t>Broadcast list opens with status filters and New Broadcast starts the wizard</t>
+  </si>
+  <si>
+    <t>Registered beta test account (config\.env). User is signed in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the Broadcasts tab.
+2. Read the count and filter chips.
+3. Tap New Broadcast.</t>
+  </si>
+  <si>
+    <t>Test account from config\.env.</t>
+  </si>
+  <si>
+    <t>"N broadcasts" header equal to the "All" chip; chips All / Draft / Scheduled / Sending / Sent / Failed. New Broadcast opens "Step 1 of 3 · Audience".</t>
+  </si>
+  <si>
+    <t>Can't call getText on element with selector "android=new UiSelector().textMatches("[0-9,]+ broadcasts?")" because element wasn't found</t>
+  </si>
+  <si>
+    <t>Screenshot: MBRD-001_Broadcast_list_opens_with_status_filters_and_New_Broadcast_starts_the_w/screenshot.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/smoke/broadcasts.spec.ts
+Last result: FAIL on 31-Oct-2026, run 20261031-133943-full.</t>
+  </si>
+  <si>
+    <t>TS-MBRD-02</t>
+  </si>
+  <si>
+    <t>Step 1: details and audience</t>
+  </si>
+  <si>
+    <t>MBRD-002</t>
+  </si>
+  <si>
+    <t>Step 1 starts with no audience chosen and the first connected number as sender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registered beta test account (config\.env).
+App restarted signed in.
+Broadcasts &gt; New Broadcast is open on step 1 (Audience).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Look at the AUDIENCE options.
+2. Open "Send from".</t>
+  </si>
+  <si>
+    <t>Test account from config\.env. Broadcast name: QA_Mobile_Draft_&lt;timestamp&gt;. Audience: Tags = BROADCAST_TAG. Template: BROADCAST_TEMPLATE (call_phone_message).</t>
+  </si>
+  <si>
+    <t>All contacts / Saved list / Segment / Tags all unselected; "All contacts" shows how many contacts it would reach. "Send from" lists the connected numbers and defaults to the first.</t>
+  </si>
+  <si>
+    <t>WebDriverError: java.util.ArrayList$ListItr cannot be cast to org.eclipse.wst.xml.xpath2.processor.internal.types.NodeType. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem. when running "elements" with method "POST"</t>
+  </si>
+  <si>
+    <t>Screenshot: MBRD-002_Step_1_starts_with_no_audience_chosen_and_the_first_connected_number_as/screenshot.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/broadcast-wizard.spec.ts
+Last result: FAIL on 31-Oct-2026, run 20261031-133943-full.</t>
+  </si>
+  <si>
+    <t>MBRD-003</t>
+  </si>
+  <si>
+    <t>Step 1 blocks Next without a name or an audience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Choose Tags without adding a tag.
+2. Leave the name empty.
+3. Tap Next.</t>
+  </si>
+  <si>
+    <t>Name: empty. Tags: none.</t>
+  </si>
+  <si>
+    <t>Stays on step 1 with "Enter at least 2 characters." and "Add at least one tag."</t>
+  </si>
+  <si>
+    <t>tag error: expected false to equal true</t>
+  </si>
+  <si>
+    <t>Screenshot: MBRD-003_Step_1_blocks_Next_without_a_name_or_an_audience/screenshot.png</t>
+  </si>
+  <si>
+    <t>MBRD-004</t>
+  </si>
+  <si>
+    <t>A one-character name is rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a one-character name.
+2. Tap Next.</t>
+  </si>
+  <si>
+    <t>Name: Q</t>
+  </si>
+  <si>
+    <t>Stays on step 1 with "Enter at least 2 characters."</t>
+  </si>
+  <si>
+    <t>One-character name rejected.</t>
+  </si>
+  <si>
+    <t>Run report: 20261031-133943-full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/broadcast-wizard.spec.ts
+Last result: PASS on 31-Oct-2026, run 20261031-133943-full.</t>
+  </si>
+  <si>
+    <t>MBRD-005</t>
+  </si>
+  <si>
+    <t>Saved list and Segment pickers offer named audiences with their sizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Choose Saved list and open the list picker.
+2. Choose Segment, open the picker and pick the smallest segment.</t>
+  </si>
+  <si>
+    <t>Each picker lists "&lt;name&gt; (&lt;count&gt;)". After picking a segment, "&lt;count&gt; contacts match." agrees with the picker.</t>
+  </si>
+  <si>
+    <t>waitUntil condition failed with the following reason: WebDriverError: java.util.ArrayList$ListItr cannot be cast to org.eclipse.wst.xml.xpath2.processor.internal.types.NodeType. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem. when running "elements" with method "POST"</t>
+  </si>
+  <si>
+    <t>Screenshot: MBRD-005_Saved_list_and_Segment_pickers_offer_named_audiences_with_their_sizes/screenshot.png</t>
+  </si>
+  <si>
+    <t>TS-MBRD-03</t>
+  </si>
+  <si>
+    <t>Step 2: template</t>
+  </si>
+  <si>
+    <t>MBRD-006</t>
+  </si>
+  <si>
+    <t>Step 2 requires a template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete step 1.
+2. Tap Next on step 2 without choosing a template.</t>
+  </si>
+  <si>
+    <t>Stays on step 2 with "Pick a template."</t>
+  </si>
+  <si>
+    <t>"Pick a template." shown.</t>
+  </si>
+  <si>
+    <t>MBRD-007</t>
+  </si>
+  <si>
+    <t>Template search is case-insensitive and reports no match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the template picker.
+2. Search the template name in upper case.
+3. Search a name that does not exist.</t>
+  </si>
+  <si>
+    <t>Search: CALL_PHONE_MESSAGE, then qa_no_such_template_zz</t>
+  </si>
+  <si>
+    <t>Upper-case search finds call_phone_message; the unknown name shows "No templates found" and "Try another name."</t>
+  </si>
+  <si>
+    <t>element ("~Search templates") still not displayed after 15000ms</t>
+  </si>
+  <si>
+    <t>Screenshot: MBRD-007_Template_search_is_case-insensitive_and_reports_no_match/screenshot.png</t>
+  </si>
+  <si>
+    <t>MBRD-008</t>
+  </si>
+  <si>
+    <t>Choosing an approved template shows its status and a WhatsApp preview</t>
+  </si>
+  <si>
+    <t>1. Choose call_phone_message.</t>
+  </si>
+  <si>
+    <t>Template shows Marketing / Approved / English and a WhatsApp preview of the message.</t>
+  </si>
+  <si>
+    <t>Approved status and preview shown.</t>
+  </si>
+  <si>
+    <t>Screenshot: screenshots/MBRD-008_template_preview.png</t>
+  </si>
+  <si>
+    <t>TS-MBRD-04</t>
+  </si>
+  <si>
+    <t>Step 3: review and confirmation</t>
+  </si>
+  <si>
+    <t>MBRD-009</t>
+  </si>
+  <si>
+    <t>Review summarises the choices, defaults to Send now and asks before sending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete steps 1-2 with the first sender, Tags and call_phone_message.
+2. Read the review.
+3. Tap Send Broadcast.
+4. Tap Cancel.</t>
+  </si>
+  <si>
+    <t>Review shows Audience "Tags: &lt;tag&gt;", the template, the sender number; "Send now" is selected with "Sending starts as soon as you confirm." Send Broadcast asks "Send this broadcast?" naming the audience; Cancel returns to the review without sending.</t>
+  </si>
+  <si>
+    <t>Screenshot: MBRD-009_Review_summarises_the_choices_defaults_to_Send_now_and_asks_before_send/screenshot.png</t>
+  </si>
+  <si>
+    <t>MBRD-010</t>
+  </si>
+  <si>
+    <t>Back keeps the entries of earlier steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reach the review.
+2. Tap Back twice.</t>
+  </si>
+  <si>
+    <t>The template and then the name and audience are still filled in.</t>
+  </si>
+  <si>
+    <t>Screenshot: MBRD-010_Back_keeps_the_entries_of_earlier_steps/screenshot.png</t>
+  </si>
+  <si>
+    <t>MBRD-011</t>
+  </si>
+  <si>
+    <t>Closing asks to discard, Cancel keeps editing and Discard saves nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a name.
+2. Tap Close, then Cancel.
+3. Tap Close, then Discard.</t>
+  </si>
+  <si>
+    <t>"Discard this broadcast?" with "This broadcast is not saved yet."; Cancel stays in the wizard; Discard returns to the list and the broadcast is not listed.</t>
+  </si>
+  <si>
+    <t>Test skipped due to failure in hook ""before each" hook: wrappedHook for "MBRD-011 Closing asks to discard, Cancel keeps editing and Discard saves nothing"": HomePage not shown within 1000 ms</t>
+  </si>
+  <si>
+    <t>MBRD-012</t>
+  </si>
+  <si>
+    <t>Review shows how many contacts a Tags audience reaches before sending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Choose Tags = BROADCAST_TAG and complete the wizard.
+2. Read the review and the "Send this broadcast?" confirmation.
+3. Cancel.</t>
+  </si>
+  <si>
+    <t>As for All contacts and segments, the user sees how many contacts the broadcast will reach before confirming.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test skipped due to failure in hook ""before each" hook: wrappedHook for "MBRD-011 Closing asks to discard, Cancel keeps editing and Discard saves nothing"": HomePage not shown within 1000 ms
+Defect: MBRD-D01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/broadcast-wizard.spec.ts
+Last result: FAIL on 31-Oct-2026, run 20261031-133943-full, defect MBRD-D01.</t>
+  </si>
+  <si>
+    <t>TS-MBRD-05</t>
+  </si>
+  <si>
+    <t>Create and send a broadcast</t>
+  </si>
+  <si>
+    <t>MBRD-020</t>
+  </si>
+  <si>
+    <t>Create and send a broadcast to the allowlisted tag, then check its recipients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registered beta test account (config\.env).
+Each BROADCAST_ALLOWLIST number has exactly one contact, carrying BROADCAST_TAG; no other contact has that tag.
+BROADCAST_SEND=true to send (otherwise the test stops before Send Now).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Contacts: search each allowlisted number; check one contact and the tag.
+2. Broadcasts &gt; New Broadcast: name, first connected number, Tags = BROADCAST_TAG, Next.
+3. Template call_phone_message, Next.
+4. Check the review and the confirmation.
+5. Send Now (once).
+6. Read the broadcast detail and the list row.</t>
+  </si>
+  <si>
+    <t>Allowlist: BROADCAST_ALLOWLIST (2 numbers, config\.env). Tag: BROADCAST_TAG. Template: call_phone_message. Sender: first connected number. Name: QA_Mobile_BC_&lt;timestamp&gt;.</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Broadcast detail opens with status Sending/Sent, "Tags: &lt;tag&gt;. 2 contacts", the template; its recipients are exactly the allowlisted numbers. The list shows "&lt;name&gt;, &lt;time&gt;, call_phone_message, 2 recipients, Sending/Sent".</t>
+  </si>
+  <si>
+    <t>Screenshot: MBRD-020_Create_and_send_a_broadcast_to_the_allowlisted_tag_then_check_its_recip/screenshot.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec: test/specs/regression/broadcast-send.spec.ts
+Last result: FAIL on 31-Oct-2026, run 20261031-133943-full.</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1645,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1691,7 +2047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1812,45 +2168,77 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="8">
-        <f>SUM(B4:B5)</f>
-        <v>43</v>
-      </c>
-      <c r="C6" s="8">
-        <f>SUM(C4:C5)</f>
-        <v>43</v>
-      </c>
-      <c r="D6" s="8">
-        <f>SUM(D4:D5)</f>
+      <c r="B6" s="5">
+        <f>C6+D6</f>
+        <v>13</v>
+      </c>
+      <c r="C6" s="5">
+        <f>COUNTIF('Broadcasts'!U2:U64,"Automation")</f>
+        <v>13</v>
+      </c>
+      <c r="D6" s="5">
+        <f>COUNTIF('Broadcasts'!U2:U64,"Manual")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="8">
-        <f>SUM(E4:E5)</f>
-        <v>19</v>
-      </c>
-      <c r="F6" s="8">
-        <f>SUM(F4:F5)</f>
-        <v>17</v>
-      </c>
-      <c r="G6" s="8">
-        <f>SUM(G4:G5)</f>
-        <v>2</v>
-      </c>
-      <c r="H6" s="8">
-        <f>SUM(H4:H5)</f>
+      <c r="E6" s="5">
+        <f>F6+G6</f>
+        <v>13</v>
+      </c>
+      <c r="F6" s="5">
+        <f>COUNTIF('Broadcasts'!Q2:Q64,"PASS")</f>
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
+        <f>COUNTIF('Broadcasts'!Q2:Q64,"FAIL")</f>
+        <v>10</v>
+      </c>
+      <c r="H6" s="5">
+        <f>B6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <f>IF(E6=0,0,F6/E6)</f>
+        <v>0.23076923076923078</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="8">
+        <f>SUM(B4:B6)</f>
+        <v>56</v>
+      </c>
+      <c r="C7" s="8">
+        <f>SUM(C4:C6)</f>
+        <v>56</v>
+      </c>
+      <c r="D7" s="8">
+        <f>SUM(D4:D6)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <f>SUM(E4:E6)</f>
+        <v>32</v>
+      </c>
+      <c r="F7" s="8">
+        <f>SUM(F4:F6)</f>
+        <v>20</v>
+      </c>
+      <c r="G7" s="8">
+        <f>SUM(G4:G6)</f>
+        <v>12</v>
+      </c>
+      <c r="H7" s="8">
+        <f>SUM(H4:H6)</f>
         <v>24</v>
       </c>
-      <c r="I6" s="9">
-        <f>IF(E6=0,0,F6/E6)</f>
-        <v>0.8947368421052632</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
+      <c r="I7" s="9">
+        <f>IF(E7=0,0,F7/E7)</f>
+        <v>0.625</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -1871,12 +2259,18 @@
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" location="#'Login'!A1"/>
     <hyperlink ref="A5" r:id="rId2" location="#'Campaigns'!A1"/>
+    <hyperlink ref="A6" r:id="rId3" location="#'Broadcasts'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1910,114 +2304,114 @@
   <sheetData>
     <row r="1" ht="62" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S1" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T1" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U1" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V1" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
@@ -2029,51 +2423,51 @@
         <v>4</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
@@ -2085,51 +2479,51 @@
         <v>4</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
@@ -2141,51 +2535,51 @@
         <v>4</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>66</v>
-      </c>
       <c r="N5" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -2197,51 +2591,51 @@
         <v>4</v>
       </c>
       <c r="V5" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
@@ -2253,51 +2647,51 @@
         <v>4</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
@@ -2309,51 +2703,51 @@
         <v>4</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -2365,51 +2759,51 @@
         <v>4</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -2421,51 +2815,51 @@
         <v>4</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -2477,51 +2871,51 @@
         <v>4</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -2533,51 +2927,51 @@
         <v>4</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -2589,51 +2983,51 @@
         <v>4</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -2645,51 +3039,51 @@
         <v>4</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -2701,51 +3095,51 @@
         <v>4</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -2757,51 +3151,51 @@
         <v>4</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -2813,51 +3207,51 @@
         <v>4</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -2869,51 +3263,51 @@
         <v>4</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
@@ -2925,51 +3319,51 @@
         <v>4</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
@@ -2981,51 +3375,51 @@
         <v>4</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
@@ -3037,51 +3431,51 @@
         <v>4</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
@@ -3093,51 +3487,51 @@
         <v>4</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
@@ -3149,51 +3543,51 @@
         <v>4</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
@@ -3205,51 +3599,51 @@
         <v>4</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O24" s="11"/>
       <c r="P24" s="11"/>
@@ -3261,51 +3655,51 @@
         <v>4</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O25" s="11"/>
       <c r="P25" s="11"/>
@@ -3317,7 +3711,7 @@
         <v>4</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="12:21" x14ac:dyDescent="0.25"/>
@@ -3438,120 +3832,120 @@
   <sheetData>
     <row r="1" ht="62" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S1" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T1" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U1" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V1" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q2" s="12" t="s">
         <v>7</v>
@@ -3560,7 +3954,7 @@
         <v>3</v>
       </c>
       <c r="S2" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T2" s="13">
         <v>46325.48961690972</v>
@@ -3569,57 +3963,57 @@
         <v>4</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q3" s="12" t="s">
         <v>7</v>
@@ -3628,7 +4022,7 @@
         <v>2</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T3" s="13">
         <v>46325.48961690972</v>
@@ -3637,57 +4031,57 @@
         <v>4</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>7</v>
@@ -3696,7 +4090,7 @@
         <v>2</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T4" s="13">
         <v>46325.48961690972</v>
@@ -3705,57 +4099,57 @@
         <v>4</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q5" s="12" t="s">
         <v>7</v>
@@ -3764,7 +4158,7 @@
         <v>2</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T5" s="13">
         <v>46325.48961690972</v>
@@ -3773,57 +4167,57 @@
         <v>4</v>
       </c>
       <c r="V5" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q6" s="12" t="s">
         <v>7</v>
@@ -3832,7 +4226,7 @@
         <v>2</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T6" s="13">
         <v>46325.48961690972</v>
@@ -3841,57 +4235,57 @@
         <v>4</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q7" s="12" t="s">
         <v>7</v>
@@ -3900,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="S7" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T7" s="13">
         <v>46325.48961690972</v>
@@ -3909,57 +4303,57 @@
         <v>4</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q8" s="12" t="s">
         <v>7</v>
@@ -3968,7 +4362,7 @@
         <v>2</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T8" s="13">
         <v>46325.48961690972</v>
@@ -3977,57 +4371,57 @@
         <v>4</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q9" s="12" t="s">
         <v>7</v>
@@ -4036,7 +4430,7 @@
         <v>2</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T9" s="13">
         <v>46325.48961690972</v>
@@ -4045,57 +4439,57 @@
         <v>4</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P10" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q10" s="12" t="s">
         <v>7</v>
@@ -4104,7 +4498,7 @@
         <v>2</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T10" s="13">
         <v>46325.48961690972</v>
@@ -4113,57 +4507,57 @@
         <v>4</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q11" s="12" t="s">
         <v>7</v>
@@ -4172,7 +4566,7 @@
         <v>2</v>
       </c>
       <c r="S11" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T11" s="13">
         <v>46325.48961690972</v>
@@ -4181,57 +4575,57 @@
         <v>4</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P12" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q12" s="12" t="s">
         <v>7</v>
@@ -4240,7 +4634,7 @@
         <v>2</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T12" s="13">
         <v>46325.48961690972</v>
@@ -4249,57 +4643,57 @@
         <v>4</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q13" s="12" t="s">
         <v>8</v>
@@ -4308,7 +4702,7 @@
         <v>4</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T13" s="13">
         <v>46325.50694328704</v>
@@ -4317,57 +4711,57 @@
         <v>4</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q14" s="12" t="s">
         <v>7</v>
@@ -4376,7 +4770,7 @@
         <v>2</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T14" s="13">
         <v>46325.48961690972</v>
@@ -4385,57 +4779,57 @@
         <v>4</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q15" s="12" t="s">
         <v>7</v>
@@ -4444,7 +4838,7 @@
         <v>2</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T15" s="13">
         <v>46325.48961690972</v>
@@ -4453,57 +4847,57 @@
         <v>4</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q16" s="12" t="s">
         <v>7</v>
@@ -4512,7 +4906,7 @@
         <v>2</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T16" s="13">
         <v>46325.48961690972</v>
@@ -4521,57 +4915,57 @@
         <v>4</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q17" s="12" t="s">
         <v>7</v>
@@ -4580,7 +4974,7 @@
         <v>2</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T17" s="13">
         <v>46325.48961690972</v>
@@ -4589,57 +4983,57 @@
         <v>4</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q18" s="12" t="s">
         <v>7</v>
@@ -4648,7 +5042,7 @@
         <v>2</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T18" s="13">
         <v>46325.48961690972</v>
@@ -4657,57 +5051,57 @@
         <v>4</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q19" s="12" t="s">
         <v>7</v>
@@ -4716,7 +5110,7 @@
         <v>2</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T19" s="13">
         <v>46325.48961690972</v>
@@ -4725,57 +5119,57 @@
         <v>4</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P20" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q20" s="12" t="s">
         <v>8</v>
@@ -4784,7 +5178,7 @@
         <v>2</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T20" s="13">
         <v>46325.48961690972</v>
@@ -4793,7 +5187,7 @@
         <v>4</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" spans="12:21" x14ac:dyDescent="0.25"/>
@@ -4906,4 +5300,1087 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:V64"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="48" customWidth="1"/>
+    <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="15" width="40" customWidth="1"/>
+    <col min="16" max="16" width="34" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="48" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="62" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="11">
+        <v>1</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T2" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="11">
+        <v>1</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T3" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" s="11">
+        <v>1</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T4" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R5" s="11">
+        <v>1</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T5" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R6" s="11">
+        <v>1</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T6" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="11">
+        <v>1</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T7" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="11">
+        <v>1</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T8" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="R9" s="11">
+        <v>1</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T9" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="11">
+        <v>1</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T10" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q11" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="11">
+        <v>1</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T11" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q12" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="11">
+        <v>1</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T12" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T13" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="11">
+        <v>1</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T14" s="13">
+        <v>46326.34009435185</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="15" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="12:21" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="12:21" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <autoFilter ref="A1:V64"/>
+  <conditionalFormatting sqref="Q2:Q64">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" sqref="L10:L64">
+      <formula1>"Smoke,Functional,Regression,UAT,API"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="L2:L64">
+      <formula1>"Smoke,Functional,Regression,UAT,API"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="M10:M64">
+      <formula1>"Positive,Negative,Boundary Value,Equivalence Partitioning,Error Handling,Validation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="M2:M64">
+      <formula1>"Positive,Negative,Boundary Value,Equivalence Partitioning,Error Handling,Validation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="Q10:Q64">
+      <formula1>"PASS,FAIL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="Q2:Q64">
+      <formula1>"PASS,FAIL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="U10:U64">
+      <formula1>"Manual,Automation,Removed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="U2:U64">
+      <formula1>"Manual,Automation,Removed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="P2" r:id="rId1"/>
+    <hyperlink ref="P3" r:id="rId2"/>
+    <hyperlink ref="P4" r:id="rId3"/>
+    <hyperlink ref="P5" r:id="rId4"/>
+    <hyperlink ref="P6" r:id="rId5"/>
+    <hyperlink ref="P7" r:id="rId6"/>
+    <hyperlink ref="P8" r:id="rId7"/>
+    <hyperlink ref="P9" r:id="rId8"/>
+    <hyperlink ref="P10" r:id="rId9"/>
+    <hyperlink ref="P11" r:id="rId10"/>
+    <hyperlink ref="P12" r:id="rId11"/>
+    <hyperlink ref="P13" r:id="rId12"/>
+    <hyperlink ref="P14" r:id="rId13"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>